--- a/Inventario_Carrinhos_conferido.xlsx
+++ b/Inventario_Carrinhos_conferido.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">O Word do carrinho azul se chama 'Carrinho 4 azul' (as etiquetas dos Chromebooks dizem carrinho 4), mas os N/S batem com o Carrinho 01 ( AZUL) do sistema, e nenhum bate com o Carrinho 04. A planilha usa o nome do sistema.</t>
   </si>
   <si>
-    <t xml:space="preserve">Modelo informado: carrinhos 05, 06, 07, 08 e 10 = Samsung Chromebook 4 cinza; carrinho 03 = Acer Chromebook R11 CB5-132T branco (o nº 26 é um Acer C731 preto); carrinho 13 = Samsung cinza (nº 1 a 16) e Acer preto (nº 17 a 28), com os Chromebooks quebrados; carrinhos 01, 02, 04, 12 e reserva = Acer Chromebook 11 C731 (N16Q13) preto (no 12, o nº 25 é um Samsung cinza; na reserva, do nº 10 ao 13 são Samsung cinza; o cabeçalho do Word da reserva diz 8 Acer + 4 Samsung, mas foram listados 9 Acer + 4 Samsung = 13). No sistema os Samsung variam de lote.</t>
+    <t xml:space="preserve">Modelo informado: carrinhos 05, 06, 07, 08 e 10 = Samsung Chromebook 4 prata; carrinho 03 = Acer Chromebook R11 CB5-132T branco (o nº 26 é um Acer C731 preto); carrinho 13 = Samsung cinza (nº 1 a 16) e Acer preto (nº 17 a 28), com os Chromebooks quebrados; carrinhos 01, 02, 04, 12 e reserva = Acer Chromebook 11 C731 preto (no 12, o nº 25 é um Samsung cinza; na reserva, do nº 10 ao 13 são Samsung cinza; o cabeçalho do Word da reserva diz 8 Acer + 4 Samsung, mas foram listados 9 Acer + 4 Samsung = 13). No sistema os Samsung variam de lote.</t>
   </si>
   <si>
     <t xml:space="preserve">As hipóteses nas observações são palpites: confirme na etiqueta do equipamento. Linhas em amarelo precisam de conferência.</t>
@@ -505,7 +505,7 @@
     <t xml:space="preserve">NXH0HAL001832D5BB39501</t>
   </si>
   <si>
-    <t xml:space="preserve">Acer Chromebook 11 C731 (N16Q13) preto</t>
+    <t xml:space="preserve">Acer Chromebook 11 C731 preto</t>
   </si>
   <si>
     <t xml:space="preserve">NXH0HAL001832D69D19501</t>
@@ -874,7 +874,7 @@
     <t xml:space="preserve">09S29QAR109567E</t>
   </si>
   <si>
-    <t xml:space="preserve">Samsung Chromebook 4 cinza</t>
+    <t xml:space="preserve">Samsung Chromebook 4 prata</t>
   </si>
   <si>
     <t xml:space="preserve">09S29QANC07347V</t>
@@ -1837,7 +1837,7 @@
     <t xml:space="preserve">09S29QBR711970</t>
   </si>
   <si>
-    <t xml:space="preserve">Samsung Chromebook 4 cinza registrado no Carrinho 03 (carrinho dos Acer brancos) e que não está no Word. Pode ser o cinza que um professor recebeu na troca pelo branco. Ele aparece no Word dos Chromebooks quebrados (computador 7), então provavelmente está lá e só falta atualizar a localização no sistema.</t>
+    <t xml:space="preserve">Samsung Chromebook 4 prata registrado no Carrinho 03 (carrinho dos Acer brancos) e que não está no Word. Pode ser o cinza que um professor recebeu na troca pelo branco. Ele aparece no Word dos Chromebooks quebrados (computador 7), então provavelmente está lá e só falta atualizar a localização no sistema.</t>
   </si>
   <si>
     <t xml:space="preserve">Registrado na reserva, mas não está no Word. Pode ser o par do computador 2 do Word (…D1F789501), se foi ditado errado: conferir a etiqueta.</t>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G13" s="11" t="str">
         <f aca="false">Conferência!G152</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H13" s="11" t="str">
         <f aca="false">Conferência!H152</f>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="G14" s="11" t="str">
         <f aca="false">Conferência!G296</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H14" s="11" t="str">
         <f aca="false">Conferência!H296</f>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="G15" s="11" t="str">
         <f aca="false">Conferência!G297</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H15" s="11" t="str">
         <f aca="false">Conferência!H297</f>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G16" s="11" t="str">
         <f aca="false">Conferência!G298</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H16" s="11" t="str">
         <f aca="false">Conferência!H298</f>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G17" s="11" t="str">
         <f aca="false">Conferência!G299</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H17" s="11" t="str">
         <f aca="false">Conferência!H299</f>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="G18" s="11" t="str">
         <f aca="false">Conferência!G300</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H18" s="11" t="str">
         <f aca="false">Conferência!H300</f>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G19" s="11" t="str">
         <f aca="false">Conferência!G301</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H19" s="11" t="str">
         <f aca="false">Conferência!H301</f>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G20" s="11" t="str">
         <f aca="false">Conferência!G302</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H20" s="11" t="str">
         <f aca="false">Conferência!H302</f>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="G21" s="11" t="str">
         <f aca="false">Conferência!G303</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H21" s="11" t="str">
         <f aca="false">Conferência!H303</f>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="G22" s="11" t="str">
         <f aca="false">Conferência!G304</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H22" s="11" t="str">
         <f aca="false">Conferência!H304</f>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="G23" s="11" t="str">
         <f aca="false">Conferência!G305</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H23" s="11" t="str">
         <f aca="false">Conferência!H305</f>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G24" s="11" t="str">
         <f aca="false">Conferência!G306</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H24" s="11" t="str">
         <f aca="false">Conferência!H306</f>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="G30" s="11" t="str">
         <f aca="false">Conferência!G82</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H30" s="11" t="str">
         <f aca="false">Conferência!H82</f>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="G31" s="11" t="str">
         <f aca="false">Conferência!G97</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H31" s="11" t="str">
         <f aca="false">Conferência!H97</f>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="G32" s="11" t="str">
         <f aca="false">Conferência!G100</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H32" s="11" t="str">
         <f aca="false">Conferência!H100</f>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="G33" s="11" t="str">
         <f aca="false">Conferência!G101</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H33" s="11" t="str">
         <f aca="false">Conferência!H101</f>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="G34" s="11" t="str">
         <f aca="false">Conferência!G103</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H34" s="11" t="str">
         <f aca="false">Conferência!H103</f>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="G35" s="11" t="str">
         <f aca="false">Conferência!G33</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H35" s="11" t="str">
         <f aca="false">Conferência!H33</f>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="G36" s="11" t="str">
         <f aca="false">Conferência!G114</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H36" s="11" t="str">
         <f aca="false">Conferência!H114</f>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="G37" s="11" t="str">
         <f aca="false">Conferência!G241</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H37" s="11" t="str">
         <f aca="false">Conferência!H241</f>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G38" s="11" t="str">
         <f aca="false">Conferência!G309</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H38" s="11" t="str">
         <f aca="false">Conferência!H309</f>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G39" s="11" t="str">
         <f aca="false">Conferência!G310</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H39" s="11" t="str">
         <f aca="false">Conferência!H310</f>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="G40" s="11" t="str">
         <f aca="false">Conferência!G311</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H40" s="11" t="str">
         <f aca="false">Conferência!H311</f>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="G41" s="11" t="str">
         <f aca="false">Conferência!G312</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H41" s="11" t="str">
         <f aca="false">Conferência!H312</f>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="G42" s="11" t="str">
         <f aca="false">Conferência!G314</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H42" s="11" t="str">
         <f aca="false">Conferência!H314</f>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="G43" s="11" t="str">
         <f aca="false">Conferência!G315</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H43" s="11" t="str">
         <f aca="false">Conferência!H315</f>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G44" s="11" t="str">
         <f aca="false">Conferência!G316</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H44" s="11" t="str">
         <f aca="false">Conferência!H316</f>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="G45" s="11" t="str">
         <f aca="false">Conferência!G317</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H45" s="11" t="str">
         <f aca="false">Conferência!H317</f>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G46" s="11" t="str">
         <f aca="false">Conferência!G318</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H46" s="11" t="str">
         <f aca="false">Conferência!H318</f>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="G47" s="11" t="str">
         <f aca="false">Conferência!G319</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H47" s="11" t="str">
         <f aca="false">Conferência!H319</f>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="G48" s="11" t="str">
         <f aca="false">Conferência!G320</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H48" s="11" t="str">
         <f aca="false">Conferência!H320</f>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G49" s="11" t="str">
         <f aca="false">Conferência!G321</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H49" s="11" t="str">
         <f aca="false">Conferência!H321</f>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="G50" s="11" t="str">
         <f aca="false">Conferência!G322</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H50" s="11" t="str">
         <f aca="false">Conferência!H322</f>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="G51" s="11" t="str">
         <f aca="false">Conferência!G323</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H51" s="11" t="str">
         <f aca="false">Conferência!H323</f>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="G52" s="11" t="str">
         <f aca="false">Conferência!G325</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H52" s="11" t="str">
         <f aca="false">Conferência!H325</f>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="G53" s="11" t="str">
         <f aca="false">Conferência!G326</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H53" s="11" t="str">
         <f aca="false">Conferência!H326</f>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G54" s="11" t="str">
         <f aca="false">Conferência!G327</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H54" s="11" t="str">
         <f aca="false">Conferência!H327</f>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="G55" s="11" t="str">
         <f aca="false">Conferência!G328</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H55" s="11" t="str">
         <f aca="false">Conferência!H328</f>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="G56" s="11" t="str">
         <f aca="false">Conferência!G329</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H56" s="11" t="str">
         <f aca="false">Conferência!H329</f>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="G57" s="11" t="str">
         <f aca="false">Conferência!G330</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H57" s="11" t="str">
         <f aca="false">Conferência!H330</f>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="G58" s="11" t="str">
         <f aca="false">Conferência!G331</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H58" s="11" t="str">
         <f aca="false">Conferência!H331</f>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="G59" s="11" t="str">
         <f aca="false">Conferência!G332</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H59" s="11" t="str">
         <f aca="false">Conferência!H332</f>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="G60" s="11" t="str">
         <f aca="false">Conferência!G334</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H60" s="11" t="str">
         <f aca="false">Conferência!H334</f>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="G61" s="11" t="str">
         <f aca="false">Conferência!G335</f>
-        <v>Acer Chromebook 11 C731 (N16Q13) preto</v>
+        <v>Acer Chromebook 11 C731 preto</v>
       </c>
       <c r="H61" s="11" t="str">
         <f aca="false">Conferência!H335</f>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="G62" s="11" t="str">
         <f aca="false">Conferência!G336</f>
-        <v>Samsung Chromebook 4 cinza</v>
+        <v>Samsung Chromebook 4 prata</v>
       </c>
       <c r="H62" s="11" t="str">
         <f aca="false">Conferência!H336</f>
@@ -19347,7 +19347,7 @@
         <v>382852</v>
       </c>
       <c r="G308" s="4" t="s">
-        <v>155</v>
+        <v>278</v>
       </c>
       <c r="H308" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Sistema!$F$2:$F$421,MATCH(D308,Sistema!$G$2:$G$421,0)),"Não encontrado")</f>
